--- a/data/trans_dic/IP19C07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por ortodoncia</t>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 34,1</t>
+          <t>6,07; 33,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 28,83</t>
+          <t>2,66; 27,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 27,66</t>
+          <t>5,72; 27,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 22,83</t>
+          <t>4,69; 22,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 26,73</t>
+          <t>3,05; 25,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 27,37</t>
+          <t>5,45; 29,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 25,49</t>
+          <t>4,23; 24,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,29</t>
+          <t>1,45; 14,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 22,66</t>
+          <t>6,93; 23,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 22,88</t>
+          <t>6,06; 22,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 21,95</t>
+          <t>7,07; 21,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 13,72</t>
+          <t>3,77; 14,44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,4</t>
+          <t>1,14; 10,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 12,97</t>
+          <t>1,26; 11,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 17,64</t>
+          <t>2,78; 18,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 21,19</t>
+          <t>6,13; 20,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,85</t>
+          <t>1,0; 10,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 15,69</t>
+          <t>3,33; 14,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 19,17</t>
+          <t>3,9; 18,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,64</t>
+          <t>2,11; 8,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,53</t>
+          <t>3,52; 10,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,56</t>
+          <t>1,85; 10,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 17,07</t>
+          <t>6,15; 16,26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,26; 37,21</t>
+          <t>13,22; 37,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 31,84</t>
+          <t>10,27; 32,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,71</t>
+          <t>0,0; 15,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 20,13</t>
+          <t>1,97; 16,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,67; 31,96</t>
+          <t>10,78; 32,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 27,11</t>
+          <t>6,88; 27,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 30,47</t>
+          <t>14,54; 31,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 26,31</t>
+          <t>11,12; 25,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,45</t>
+          <t>0,93; 8,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 27,88</t>
+          <t>7,95; 27,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 16,29</t>
+          <t>2,61; 16,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 23,63</t>
+          <t>3,13; 22,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 31,11</t>
+          <t>11,15; 33,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 17,29</t>
+          <t>1,51; 15,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 25,12</t>
+          <t>11,56; 25,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 12,78</t>
+          <t>3,04; 12,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 10,82</t>
+          <t>1,31; 11,25</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,33</t>
+          <t>0,0; 18,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,25</t>
+          <t>0,0; 13,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 31,96</t>
+          <t>4,28; 34,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,45</t>
+          <t>0,0; 16,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 25,06</t>
+          <t>2,67; 23,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 45,98</t>
+          <t>10,13; 46,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,92</t>
+          <t>0,0; 10,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,82</t>
+          <t>1,31; 11,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,27</t>
+          <t>2,46; 15,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,58; 32,61</t>
+          <t>10,09; 34,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,89</t>
+          <t>1,0; 10,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 27,19</t>
+          <t>5,23; 27,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,67; 28,02</t>
+          <t>7,29; 27,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 22,94</t>
+          <t>4,28; 23,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,98</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 29,07</t>
+          <t>6,6; 27,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 23,17</t>
+          <t>5,41; 24,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,02</t>
+          <t>0,0; 11,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,24; 23,66</t>
+          <t>8,34; 24,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 22,69</t>
+          <t>8,16; 22,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,59; 13,79</t>
+          <t>3,56; 13,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,27; 21,81</t>
+          <t>8,27; 21,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,69; 24,09</t>
+          <t>8,64; 23,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 18,96</t>
+          <t>5,76; 19,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 17,13</t>
+          <t>4,87; 17,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,93</t>
+          <t>4,24; 16,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,29</t>
+          <t>7,53; 21,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,24</t>
+          <t>1,15; 10,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 13,51</t>
+          <t>3,97; 13,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,8; 16,25</t>
+          <t>6,82; 16,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 19,88</t>
+          <t>10,04; 19,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 12,95</t>
+          <t>4,17; 12,46</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,99</t>
+          <t>5,26; 12,81</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,43; 16,93</t>
+          <t>5,58; 16,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,39</t>
+          <t>1,57; 9,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,55; 13,67</t>
+          <t>3,96; 13,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,36</t>
+          <t>0,97; 9,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 11,48</t>
+          <t>2,77; 11,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,54</t>
+          <t>1,87; 10,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,24; 17,51</t>
+          <t>6,06; 18,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 13,54</t>
+          <t>3,96; 14,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 12,58</t>
+          <t>5,17; 12,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,88</t>
+          <t>2,24; 8,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,62</t>
+          <t>6,11; 13,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,68</t>
+          <t>3,52; 9,82</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,37; 15,09</t>
+          <t>9,47; 15,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,55</t>
+          <t>7,26; 12,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,05</t>
+          <t>5,88; 11,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,53</t>
+          <t>5,92; 10,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,91</t>
+          <t>7,5; 12,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,71</t>
+          <t>7,66; 12,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,05</t>
+          <t>4,04; 7,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,86</t>
+          <t>4,0; 8,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,06</t>
+          <t>9,32; 13,24</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,88</t>
+          <t>8,05; 11,8</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,62</t>
+          <t>5,43; 8,6</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,24</t>
+          <t>5,21; 8,17</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2758</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4364</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3013</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6715</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7746</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1173; 6378</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>615; 6393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1679; 8043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1633; 7871</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>808; 6813</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1616; 8618</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1266; 7429</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>578; 5668</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3178; 10754</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3200; 11666</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4187; 12853</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2817; 10783</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8307</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2817</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4518</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7034</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7181</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5156</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>15340</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>651; 6002</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>667; 6045</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1486; 9785</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4221; 14383</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>651; 6758</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1919; 8487</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3510</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2879; 13775</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2584; 9796</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3898; 11901</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2037; 11872</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>8769; 23194</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8389</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6373</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6937</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15326</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12382</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4533; 12806</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3435; 10789</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4917</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>625; 5177</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3808; 11347</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2712; 10753</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2847</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10122; 21584</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8104; 18425</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4667</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>672; 6078</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6702</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7956</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14659</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3337; 11595</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1089; 6887</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1341; 9492</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4645; 13813</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>624; 6346</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2839</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9668; 21009</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2524; 10220</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1330; 11422</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3542</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4824</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3449</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>644; 5143</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3376</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>738; 6494</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1729; 8004</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3495</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>637; 5408</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1320; 8158</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3241; 10959</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>599; 6054</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5596</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3969</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7827</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9565</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6038</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1324; 6844</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2583; 9748</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1700; 9249</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2782</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1870; 7695</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1795; 8035</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4479</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>4478; 13069</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>5594; 15114</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2856; 10997</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2299</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9750</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7380</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5769</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9162</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>8453</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>14635</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>18912</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>9868</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>15833</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5397; 14299</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5527; 14981</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3886; 12892</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3790; 13847</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2885; 11063</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5061; 14190</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>714; 6425</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4315; 15078</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>9087; 22166</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>13171; 25934</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5396; 16128</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>9803; 23886</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>8468</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6045</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8555</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>13079</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>14600</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>11368</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>4541; 13784</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1225; 7461</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>3135; 10852</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>809; 8096</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2063; 8761</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1312; 7431</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4766; 14229</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>4035; 14331</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>8058; 19374</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3318; 11833</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>9648; 21188</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>6520; 18175</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>42898</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>34337</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>29692</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>27880</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>79125</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>70490</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>50587</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>58238</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>33248; 53716</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>25757; 43994</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>21373; 39972</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>23186; 41294</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>27139; 45993</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>28052; 47275</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>14857; 29276</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>19399; 38966</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>66442; 94353</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>58006; 85017</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>39744; 62906</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>45682; 71610</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 33,01</t>
+          <t>5,86; 31,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 27,66</t>
+          <t>4,01; 28,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 27,41</t>
+          <t>6,31; 31,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 22,61</t>
+          <t>3,92; 22,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 25,69</t>
+          <t>2,99; 23,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 29,06</t>
+          <t>4,44; 28,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 24,84</t>
+          <t>4,08; 24,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 14,22</t>
+          <t>1,48; 14,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 23,46</t>
+          <t>6,8; 23,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 22,11</t>
+          <t>5,88; 21,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 21,69</t>
+          <t>7,1; 21,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 14,44</t>
+          <t>3,4; 13,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,49</t>
+          <t>1,14; 11,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,4</t>
+          <t>1,29; 13,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 18,29</t>
+          <t>2,74; 17,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 20,89</t>
+          <t>6,26; 19,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,4</t>
+          <t>1,01; 9,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 14,73</t>
+          <t>3,24; 13,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 18,66</t>
+          <t>3,87; 19,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,02</t>
+          <t>2,11; 8,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,75</t>
+          <t>3,47; 10,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,77</t>
+          <t>1,87; 9,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,26</t>
+          <t>6,55; 17,58</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 37,34</t>
+          <t>13,68; 37,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 32,24</t>
+          <t>9,75; 33,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,12</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,27</t>
+          <t>1,96; 16,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 32,12</t>
+          <t>10,7; 31,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 27,26</t>
+          <t>7,88; 25,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,54; 31,0</t>
+          <t>15,14; 31,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,12; 25,27</t>
+          <t>10,34; 25,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,46</t>
+          <t>0,95; 8,76</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 27,63</t>
+          <t>7,69; 25,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 16,48</t>
+          <t>2,57; 16,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 22,16</t>
+          <t>2,6; 20,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 33,17</t>
+          <t>10,66; 31,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,39</t>
+          <t>1,52; 16,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 25,13</t>
+          <t>11,28; 25,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 12,31</t>
+          <t>3,35; 12,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,25</t>
+          <t>1,29; 10,29</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,42</t>
+          <t>0,0; 18,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,23</t>
+          <t>0,0; 17,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 34,18</t>
+          <t>0,0; 30,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,83</t>
+          <t>0,0; 17,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 23,5</t>
+          <t>2,55; 23,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 46,89</t>
+          <t>11,51; 48,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,09</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,11</t>
+          <t>1,31; 12,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,19</t>
+          <t>2,48; 14,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 34,13</t>
+          <t>9,93; 34,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,1</t>
+          <t>0,96; 8,97</t>
         </is>
       </c>
     </row>
@@ -1417,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 27,01</t>
+          <t>5,31; 28,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 27,52</t>
+          <t>7,64; 27,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 23,27</t>
+          <t>5,28; 23,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,6; 27,14</t>
+          <t>6,84; 29,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 24,23</t>
+          <t>4,16; 22,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,04</t>
+          <t>0,0; 13,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 24,34</t>
+          <t>7,23; 23,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 22,04</t>
+          <t>8,14; 22,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 13,69</t>
+          <t>3,67; 14,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,27; 21,9</t>
+          <t>8,16; 21,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 23,42</t>
+          <t>8,72; 23,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 19,11</t>
+          <t>5,24; 17,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 17,81</t>
+          <t>4,63; 17,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 16,26</t>
+          <t>4,15; 15,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 21,13</t>
+          <t>7,71; 21,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,37</t>
+          <t>1,13; 10,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 13,87</t>
+          <t>4,16; 13,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 16,63</t>
+          <t>7,33; 16,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 19,78</t>
+          <t>10,05; 19,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,46</t>
+          <t>4,49; 12,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 12,81</t>
+          <t>5,36; 12,81</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,58; 16,95</t>
+          <t>6,19; 17,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,58</t>
+          <t>1,59; 9,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,96; 13,69</t>
+          <t>3,58; 13,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,72</t>
+          <t>0,94; 9,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 11,77</t>
+          <t>2,74; 11,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,6</t>
+          <t>1,86; 10,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,06; 18,09</t>
+          <t>6,47; 17,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,96; 14,08</t>
+          <t>3,97; 14,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,17; 12,44</t>
+          <t>5,44; 13,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,0</t>
+          <t>2,2; 8,13</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,11; 13,42</t>
+          <t>5,62; 13,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,82</t>
+          <t>3,4; 10,09</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,47; 15,31</t>
+          <t>9,73; 15,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,4</t>
+          <t>7,29; 12,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 11,0</t>
+          <t>5,93; 11,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,54</t>
+          <t>5,64; 10,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,71</t>
+          <t>7,79; 12,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,92</t>
+          <t>7,58; 12,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,96</t>
+          <t>3,94; 7,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,04</t>
+          <t>4,12; 7,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,24</t>
+          <t>9,35; 13,2</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,8</t>
+          <t>8,09; 11,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,6</t>
+          <t>5,57; 8,63</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,17</t>
+          <t>5,23; 8,22</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1173; 6378</t>
+          <t>1131; 6056</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>615; 6393</t>
+          <t>927; 6549</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1679; 8043</t>
+          <t>1852; 9114</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1633; 7871</t>
+          <t>1366; 7659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>808; 6813</t>
+          <t>792; 6149</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1616; 8618</t>
+          <t>1316; 8395</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1266; 7429</t>
+          <t>1221; 7256</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>578; 5668</t>
+          <t>592; 5700</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3178; 10754</t>
+          <t>3119; 10685</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3200; 11666</t>
+          <t>3102; 11378</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4187; 12853</t>
+          <t>4206; 13005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2817; 10783</t>
+          <t>2538; 10192</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>651; 6002</t>
+          <t>654; 6636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>667; 6045</t>
+          <t>683; 7269</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1486; 9785</t>
+          <t>1469; 9322</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4221; 14383</t>
+          <t>4312; 13440</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>651; 6758</t>
+          <t>655; 6494</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1919; 8487</t>
+          <t>1865; 7986</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3510</t>
+          <t>0; 4535</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2879; 13775</t>
+          <t>2858; 14051</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2584; 9796</t>
+          <t>2578; 10359</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3898; 11901</t>
+          <t>3845; 12144</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2037; 11872</t>
+          <t>2060; 10777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8769; 23194</t>
+          <t>9348; 25078</t>
         </is>
       </c>
     </row>
@@ -2625,32 +2625,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4533; 12806</t>
+          <t>4692; 12968</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3435; 10789</t>
+          <t>3262; 11236</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4917</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>625; 5177</t>
+          <t>623; 5242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3808; 11347</t>
+          <t>3781; 10986</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2712; 10753</t>
+          <t>3108; 10239</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2847</t>
+          <t>0; 2687</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10122; 21584</t>
+          <t>10542; 21756</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8104; 18425</t>
+          <t>7535; 18544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4667</t>
+          <t>0; 4338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>672; 6078</t>
+          <t>679; 6294</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3337; 11595</t>
+          <t>3227; 10764</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1089; 6887</t>
+          <t>1074; 6775</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1341; 9492</t>
+          <t>1113; 8673</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4645; 13813</t>
+          <t>4439; 13024</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>624; 6346</t>
+          <t>625; 6883</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2839</t>
+          <t>0; 3548</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9668; 21009</t>
+          <t>9432; 21187</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2524; 10220</t>
+          <t>2778; 10188</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1330; 11422</t>
+          <t>1314; 10444</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>0; 4793</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3449</t>
+          <t>0; 4460</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>644; 5143</t>
+          <t>0; 4657</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4256</t>
+          <t>0; 4368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>0; 3377</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>738; 6494</t>
+          <t>704; 6471</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1729; 8004</t>
+          <t>1965; 8356</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3495</t>
+          <t>0; 3541</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>637; 5408</t>
+          <t>638; 5985</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1320; 8158</t>
+          <t>1333; 7788</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3241; 10959</t>
+          <t>3187; 11175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>599; 6054</t>
+          <t>575; 5374</t>
         </is>
       </c>
     </row>
@@ -3249,37 +3249,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1324; 6844</t>
+          <t>1346; 7334</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2583; 9748</t>
+          <t>2708; 9754</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1700; 9249</t>
+          <t>2099; 9208</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2782</t>
+          <t>0; 2248</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1870; 7695</t>
+          <t>1939; 8271</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1795; 8035</t>
+          <t>1379; 7566</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4479</t>
+          <t>0; 5457</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,22 +3289,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4478; 13069</t>
+          <t>3884; 12413</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5594; 15114</t>
+          <t>5584; 15282</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2856; 10997</t>
+          <t>2948; 11332</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2299</t>
+          <t>0; 3210</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5397; 14299</t>
+          <t>5329; 14106</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5527; 14981</t>
+          <t>5581; 14754</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3886; 12892</t>
+          <t>3534; 12128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3790; 13847</t>
+          <t>3599; 13558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2885; 11063</t>
+          <t>2821; 10800</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5061; 14190</t>
+          <t>5181; 14415</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>714; 6425</t>
+          <t>699; 6397</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4315; 15078</t>
+          <t>4523; 14622</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9087; 22166</t>
+          <t>9775; 21707</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13171; 25934</t>
+          <t>13176; 26205</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5396; 16128</t>
+          <t>5811; 16642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9803; 23886</t>
+          <t>9993; 23882</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4541; 13784</t>
+          <t>5032; 14477</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1225; 7461</t>
+          <t>1236; 7356</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3135; 10852</t>
+          <t>2838; 10847</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>809; 8096</t>
+          <t>779; 8102</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2063; 8761</t>
+          <t>2040; 8790</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1312; 7431</t>
+          <t>1303; 7374</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4766; 14229</t>
+          <t>5086; 13821</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4035; 14331</t>
+          <t>4040; 14324</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8058; 19374</t>
+          <t>8468; 20318</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3318; 11833</t>
+          <t>3259; 12024</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9648; 21188</t>
+          <t>8873; 21137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6520; 18175</t>
+          <t>6294; 18671</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33248; 53716</t>
+          <t>34135; 53121</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25757; 43994</t>
+          <t>25853; 43860</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21373; 39972</t>
+          <t>21548; 39995</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23186; 41294</t>
+          <t>22072; 41057</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>27139; 45993</t>
+          <t>28173; 46308</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28052; 47275</t>
+          <t>27746; 46738</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14857; 29276</t>
+          <t>14488; 28954</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>19399; 38966</t>
+          <t>19975; 38241</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>66442; 94353</t>
+          <t>66619; 94096</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58006; 85017</t>
+          <t>58317; 84678</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39744; 62906</t>
+          <t>40738; 63133</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>45682; 71610</t>
+          <t>45816; 72029</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>16,3%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,93%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 31,34</t>
+          <t>3,02; 26,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 28,34</t>
+          <t>4,88; 27,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 31,06</t>
+          <t>4,33; 25,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 22,0</t>
+          <t>1,74; 15,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 23,19</t>
+          <t>6,25; 34,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 28,3</t>
+          <t>3,2; 28,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 24,26</t>
+          <t>5,79; 27,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 14,3</t>
+          <t>4,46; 24,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 23,31</t>
+          <t>6,67; 22,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 21,56</t>
+          <t>6,25; 22,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 21,95</t>
+          <t>7,03; 21,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 13,65</t>
+          <t>3,99; 14,76</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,52%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,6</t>
+          <t>1,02; 10,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,7</t>
+          <t>3,36; 15,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 17,42</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 19,52</t>
+          <t>3,92; 19,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,99</t>
+          <t>1,13; 10,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 13,86</t>
+          <t>1,26; 12,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,99</t>
+          <t>2,75; 17,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 19,03</t>
+          <t>6,8; 22,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,48</t>
+          <t>2,13; 8,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 10,97</t>
+          <t>3,47; 11,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 9,78</t>
+          <t>1,88; 10,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 17,58</t>
+          <t>6,82; 17,83</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24,46%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19,05%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 37,82</t>
+          <t>10,67; 31,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 33,58</t>
+          <t>8,23; 27,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 16,47</t>
+          <t>0,0; 6,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 31,1</t>
+          <t>13,26; 37,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 25,96</t>
+          <t>8,72; 31,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>1,93; 19,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 31,25</t>
+          <t>14,66; 30,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 25,44</t>
+          <t>10,71; 26,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,76</t>
+          <t>0,95; 8,53</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 25,65</t>
+          <t>10,0; 31,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 16,21</t>
+          <t>1,51; 17,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 20,24</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 31,28</t>
+          <t>8,72; 27,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 16,69</t>
+          <t>2,59; 16,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>3,43; 25,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 25,34</t>
+          <t>11,7; 25,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 12,27</t>
+          <t>3,12; 12,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,29</t>
+          <t>1,72; 11,9</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25,38%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,22%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>13,38%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>25,38%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,3</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,11</t>
+          <t>2,91; 25,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,95</t>
+          <t>10,09; 45,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,27</t>
+          <t>0,0; 12,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>0,0; 16,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 23,42</t>
+          <t>0,0; 13,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 48,96</t>
+          <t>4,28; 31,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 17,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,3</t>
+          <t>1,32; 12,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,5</t>
+          <t>2,55; 14,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 34,8</t>
+          <t>8,58; 32,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,97</t>
+          <t>0,99; 10,29</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13,3%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15,8%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,31; 28,94</t>
+          <t>6,68; 29,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,64; 27,53</t>
+          <t>4,24; 23,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 23,17</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 29,16</t>
+          <t>5,17; 27,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 22,82</t>
+          <t>7,67; 28,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,45</t>
+          <t>4,36; 22,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 23,12</t>
+          <t>8,24; 23,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 22,28</t>
+          <t>8,32; 22,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 14,11</t>
+          <t>3,59; 13,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 5,67</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13,58%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15,24%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11,0%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 21,61</t>
+          <t>4,21; 15,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,72; 23,06</t>
+          <t>7,51; 22,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 17,98</t>
+          <t>1,15; 10,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 17,44</t>
+          <t>4,21; 14,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 15,88</t>
+          <t>8,27; 21,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 21,46</t>
+          <t>8,69; 24,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,33</t>
+          <t>5,65; 18,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 13,45</t>
+          <t>4,87; 18,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 16,28</t>
+          <t>6,8; 16,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 19,98</t>
+          <t>10,03; 19,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 12,86</t>
+          <t>4,1; 12,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 12,81</t>
+          <t>5,87; 13,91</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>4,23%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>7,63%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 17,8</t>
+          <t>2,52; 11,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,45</t>
+          <t>1,88; 10,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 13,69</t>
+          <t>6,24; 17,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,73</t>
+          <t>4,24; 13,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,81</t>
+          <t>5,43; 16,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 10,52</t>
+          <t>1,6; 9,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,47; 17,57</t>
+          <t>3,55; 13,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,97; 14,07</t>
+          <t>1,22; 9,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,05</t>
+          <t>5,47; 12,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,13</t>
+          <t>2,3; 7,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 13,39</t>
+          <t>5,88; 13,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,09</t>
+          <t>3,39; 9,51</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,14</t>
+          <t>7,67; 12,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,36</t>
+          <t>7,56; 12,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,01</t>
+          <t>4,08; 8,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,48</t>
+          <t>4,29; 8,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,8</t>
+          <t>9,37; 15,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,77</t>
+          <t>7,43; 12,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,87</t>
+          <t>5,96; 11,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,89</t>
+          <t>5,77; 10,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,2</t>
+          <t>9,16; 13,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,75</t>
+          <t>8,1; 11,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,63</t>
+          <t>5,55; 8,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,22</t>
+          <t>5,31; 8,52</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3013</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3150</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2758</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4364</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3013</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3957</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3382</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5399</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1131; 6056</t>
+          <t>801; 7087</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>927; 6549</t>
+          <t>1447; 8119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1852; 9114</t>
+          <t>1294; 7625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1366; 7659</t>
+          <t>580; 5158</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>792; 6149</t>
+          <t>1207; 6588</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1316; 8395</t>
+          <t>739; 6662</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1221; 7256</t>
+          <t>1699; 8118</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>592; 5700</t>
+          <t>1315; 7286</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3119; 10685</t>
+          <t>3058; 10386</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3102; 11378</t>
+          <t>3297; 12073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4206; 13005</t>
+          <t>4164; 13005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2538; 10192</t>
+          <t>2503; 9268</t>
         </is>
       </c>
     </row>
@@ -2286,37 +2286,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2817</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4518</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6397</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2586</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2663</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4456</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8307</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2817</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4518</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>15142</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>654; 6636</t>
+          <t>665; 7050</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>683; 7269</t>
+          <t>1937; 9041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1469; 9322</t>
+          <t>0; 3804</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4312; 13440</t>
+          <t>2717; 13207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>655; 6494</t>
+          <t>647; 5949</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1865; 7986</t>
+          <t>667; 6880</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4535</t>
+          <t>1471; 9439</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2858; 14051</t>
+          <t>4628; 15327</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2578; 10359</t>
+          <t>2602; 10555</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3845; 12144</t>
+          <t>3845; 12761</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2060; 10777</t>
+          <t>2069; 11638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9348; 25078</t>
+          <t>9357; 24476</t>
         </is>
       </c>
     </row>
@@ -2499,32 +2499,32 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6937</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8389</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6373</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>836</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6937</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6009</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2412</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4692; 12968</t>
+          <t>3771; 11292</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3262; 11236</t>
+          <t>3245; 10693</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>623; 5242</t>
+          <t>0; 2420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3781; 10986</t>
+          <t>4549; 12759</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3108; 10239</t>
+          <t>2919; 10653</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4133</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2687</t>
+          <t>608; 6252</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10542; 21756</t>
+          <t>10204; 21215</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7535; 18544</t>
+          <t>7806; 19182</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4338</t>
+          <t>0; 4847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>679; 6294</t>
+          <t>639; 5720</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,62 +2765,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7956</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6702</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3212</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3942</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7956</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2319</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4497</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14659</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>14659</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5531</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4950</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3227; 10764</t>
+          <t>4162; 12956</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1074; 6775</t>
+          <t>623; 7130</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1113; 8673</t>
+          <t>0; 3114</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4439; 13024</t>
+          <t>3660; 11698</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>625; 6883</t>
+          <t>1081; 6809</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3548</t>
+          <t>1553; 11341</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9432; 21187</t>
+          <t>9779; 21001</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2778; 10188</t>
+          <t>2592; 10610</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1314; 10444</t>
+          <t>1707; 11848</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1368</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>689</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2520</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4793</t>
+          <t>0; 2873</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4460</t>
+          <t>803; 6925</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4657</t>
+          <t>1721; 7848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4368</t>
+          <t>0; 4086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3377</t>
+          <t>0; 4277</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>704; 6471</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1965; 8356</t>
+          <t>645; 4808</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3541</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>638; 5985</t>
+          <t>643; 6237</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1333; 7788</t>
+          <t>1368; 7660</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3187; 11175</t>
+          <t>2756; 10470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>575; 5374</t>
+          <t>594; 6179</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3969</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3370</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5596</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4559</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4457</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1478</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>505</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1346; 7334</t>
+          <t>1894; 8245</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2708; 9754</t>
+          <t>1405; 7684</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2099; 9208</t>
+          <t>0; 5283</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2248</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1939; 8271</t>
+          <t>1310; 6890</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1379; 7566</t>
+          <t>2718; 9926</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5457</t>
+          <t>1731; 9117</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2614</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3884; 12413</t>
+          <t>4427; 12707</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5584; 15282</t>
+          <t>5706; 15561</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2948; 11332</t>
+          <t>2886; 11076</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3210</t>
+          <t>0; 2958</t>
         </is>
       </c>
     </row>
@@ -3321,37 +3321,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5769</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9162</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8809</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>8866</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>9750</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>7419</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7380</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5769</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>9162</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2450</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>16369</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5329; 14106</t>
+          <t>2866; 10835</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5581; 14754</t>
+          <t>5046; 14972</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3534; 12128</t>
+          <t>713; 6341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3599; 13558</t>
+          <t>4317; 15318</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2821; 10800</t>
+          <t>5396; 14241</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5181; 14415</t>
+          <t>5558; 15410</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>699; 6397</t>
+          <t>3811; 12785</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4523; 14622</t>
+          <t>3703; 13700</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9775; 21707</t>
+          <t>9069; 21661</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13176; 26205</t>
+          <t>13150; 26065</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5811; 16642</t>
+          <t>5307; 16757</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9993; 23882</t>
+          <t>10484; 24848</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,44 +3597,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>8555</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>8720</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>8468</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>6045</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3284</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>4612</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>3366</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>8555</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8084</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>13079</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>12087</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5032; 14477</t>
+          <t>1876; 8541</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1236; 7356</t>
+          <t>1317; 7390</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2838; 10847</t>
+          <t>4909; 13771</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>779; 8102</t>
+          <t>4596; 14901</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2040; 8790</t>
+          <t>4417; 13764</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1303; 7374</t>
+          <t>1245; 7312</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5086; 13821</t>
+          <t>2817; 10835</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4040; 14324</t>
+          <t>1118; 9017</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8468; 20318</t>
+          <t>8523; 19598</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3259; 12024</t>
+          <t>3396; 11663</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8873; 21137</t>
+          <t>9284; 21507</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6294; 18671</t>
+          <t>6767; 19017</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>27914</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>42898</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>34337</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>36153</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59383</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>34135; 53121</t>
+          <t>27746; 46699</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25853; 43860</t>
+          <t>27652; 46512</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21548; 39995</t>
+          <t>15014; 29636</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22072; 41057</t>
+          <t>19800; 38307</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28173; 46308</t>
+          <t>32872; 52969</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27746; 46738</t>
+          <t>26370; 44516</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14488; 28954</t>
+          <t>21653; 40170</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>19975; 38241</t>
+          <t>22847; 42910</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>66619; 94096</t>
+          <t>65315; 93057</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58317; 84678</t>
+          <t>58351; 85608</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40738; 63133</t>
+          <t>40567; 63057</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>45816; 72029</t>
+          <t>45499; 73060</t>
         </is>
       </c>
     </row>
